--- a/fund_tracker/Inputs/Weightage.xlsx
+++ b/fund_tracker/Inputs/Weightage.xlsx
@@ -1,21 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8261f3b7260beb32/Documents/Emkay Analytics Tool/fund_tracker/Inputs/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_23F921EDC12BCC80257B64A836B57D2455943123" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CE7032EE-BFF3-4EFC-92F2-6DD35EEE2A2A}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -38,6 +32,9 @@
   </si>
   <si>
     <t>Current Weight</t>
+  </si>
+  <si>
+    <t>CBTWRR</t>
   </si>
   <si>
     <t>ABCD01</t>
@@ -117,27 +114,16 @@
   <si>
     <t>ITC</t>
   </si>
-  <si>
-    <t>CBAIFMF</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -153,7 +139,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -161,30 +147,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -192,21 +160,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -244,7 +204,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -278,7 +238,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -313,10 +272,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -489,3793 +447,3793 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F193"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:6">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="2">
+    <row r="2" spans="1:6">
+      <c r="A2" s="1">
         <v>45869</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F2">
         <v>19.61</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="2">
+    <row r="3" spans="1:6">
+      <c r="A3" s="1">
         <v>45869</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F3">
         <v>44.84</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="2">
+    <row r="4" spans="1:6">
+      <c r="A4" s="1">
         <v>45869</v>
       </c>
       <c r="B4" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F4">
         <v>1.76</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="2">
+    <row r="5" spans="1:6">
+      <c r="A5" s="1">
         <v>45869</v>
       </c>
       <c r="B5" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F5">
         <v>13.27</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="2">
+    <row r="6" spans="1:6">
+      <c r="A6" s="1">
         <v>45869</v>
       </c>
       <c r="B6" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F6">
         <v>1.5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="2">
+    <row r="7" spans="1:6">
+      <c r="A7" s="1">
         <v>45869</v>
       </c>
       <c r="B7" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F7">
         <v>13.72</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="2">
+    <row r="8" spans="1:6">
+      <c r="A8" s="1">
         <v>45869</v>
       </c>
       <c r="B8" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F8">
         <v>5.31</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="2">
+    <row r="9" spans="1:6">
+      <c r="A9" s="1">
         <v>45900</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C9" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F9">
         <v>20.04</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="2">
+    <row r="10" spans="1:6">
+      <c r="A10" s="1">
         <v>45900</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C10" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F10">
         <v>44.25</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="2">
+    <row r="11" spans="1:6">
+      <c r="A11" s="1">
         <v>45900</v>
       </c>
       <c r="B11" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C11" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F11">
         <v>0.1</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="2">
+    <row r="12" spans="1:6">
+      <c r="A12" s="1">
         <v>45900</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C12" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E12" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F12">
         <v>17.48</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="2">
+    <row r="13" spans="1:6">
+      <c r="A13" s="1">
         <v>45900</v>
       </c>
       <c r="B13" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C13" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F13">
-        <v>0.69</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="2">
+        <v>0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="1">
         <v>45900</v>
       </c>
       <c r="B14" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F14">
         <v>14.67</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="2">
+    <row r="15" spans="1:6">
+      <c r="A15" s="1">
         <v>45900</v>
       </c>
       <c r="B15" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C15" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F15">
         <v>2.78</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="2">
+    <row r="16" spans="1:6">
+      <c r="A16" s="1">
         <v>45930</v>
       </c>
       <c r="B16" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C16" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D16" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F16">
-        <v>19.559999999999999</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="2">
+        <v>19.56</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="1">
         <v>45930</v>
       </c>
       <c r="B17" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C17" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D17" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F17">
         <v>41.47</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="2">
+    <row r="18" spans="1:6">
+      <c r="A18" s="1">
         <v>45930</v>
       </c>
       <c r="B18" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C18" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D18" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E18" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F18">
         <v>1.98</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="2">
+    <row r="19" spans="1:6">
+      <c r="A19" s="1">
         <v>45930</v>
       </c>
       <c r="B19" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C19" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D19" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E19" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F19">
         <v>14.6</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="2">
+    <row r="20" spans="1:6">
+      <c r="A20" s="1">
         <v>45930</v>
       </c>
       <c r="B20" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C20" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D20" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E20" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F20">
         <v>5.85</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="2">
+    <row r="21" spans="1:6">
+      <c r="A21" s="1">
         <v>45930</v>
       </c>
       <c r="B21" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C21" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D21" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E21" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F21">
         <v>13.23</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="2">
+    <row r="22" spans="1:6">
+      <c r="A22" s="1">
         <v>45930</v>
       </c>
       <c r="B22" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C22" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F22">
         <v>3.3</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="2">
+    <row r="23" spans="1:6">
+      <c r="A23" s="1">
         <v>45961</v>
       </c>
       <c r="B23" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C23" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D23" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E23" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F23">
         <v>17.55</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="2">
+    <row r="24" spans="1:6">
+      <c r="A24" s="1">
         <v>45961</v>
       </c>
       <c r="B24" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C24" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D24" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E24" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F24">
         <v>45.87</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="2">
+    <row r="25" spans="1:6">
+      <c r="A25" s="1">
         <v>45961</v>
       </c>
       <c r="B25" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C25" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D25" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E25" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F25">
         <v>4.38</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="2">
+    <row r="26" spans="1:6">
+      <c r="A26" s="1">
         <v>45961</v>
       </c>
       <c r="B26" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C26" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D26" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E26" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F26">
         <v>14.44</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="2">
+    <row r="27" spans="1:6">
+      <c r="A27" s="1">
         <v>45961</v>
       </c>
       <c r="B27" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C27" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D27" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E27" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F27">
         <v>0.1</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="2">
+    <row r="28" spans="1:6">
+      <c r="A28" s="1">
         <v>45961</v>
       </c>
       <c r="B28" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C28" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D28" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E28" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F28">
         <v>12.99</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="2">
+    <row r="29" spans="1:6">
+      <c r="A29" s="1">
         <v>45961</v>
       </c>
       <c r="B29" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C29" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E29" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F29">
         <v>4.68</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="2">
+    <row r="30" spans="1:6">
+      <c r="A30" s="1">
         <v>45991</v>
       </c>
       <c r="B30" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C30" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D30" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E30" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F30">
         <v>20.99</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="2">
+    <row r="31" spans="1:6">
+      <c r="A31" s="1">
         <v>45991</v>
       </c>
       <c r="B31" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C31" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D31" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E31" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F31">
         <v>43.16</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="2">
+    <row r="32" spans="1:6">
+      <c r="A32" s="1">
         <v>45991</v>
       </c>
       <c r="B32" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C32" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D32" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E32" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F32">
         <v>0.09</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="2">
+    <row r="33" spans="1:6">
+      <c r="A33" s="1">
         <v>45991</v>
       </c>
       <c r="B33" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C33" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D33" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E33" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F33">
         <v>14.61</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="2">
+    <row r="34" spans="1:6">
+      <c r="A34" s="1">
         <v>45991</v>
       </c>
       <c r="B34" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C34" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D34" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E34" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F34">
         <v>1.29</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="2">
+    <row r="35" spans="1:6">
+      <c r="A35" s="1">
         <v>45991</v>
       </c>
       <c r="B35" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C35" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D35" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E35" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F35">
         <v>15.13</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="2">
+    <row r="36" spans="1:6">
+      <c r="A36" s="1">
         <v>45991</v>
       </c>
       <c r="B36" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C36" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E36" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F36">
-        <v>4.7300000000000004</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="2">
+        <v>4.73</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37" s="1">
         <v>46022</v>
       </c>
       <c r="B37" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C37" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D37" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E37" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F37">
-        <v>20.079999999999998</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="2">
+        <v>20.08</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38" s="1">
         <v>46022</v>
       </c>
       <c r="B38" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C38" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D38" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E38" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F38">
         <v>45.12</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="2">
+    <row r="39" spans="1:6">
+      <c r="A39" s="1">
         <v>46022</v>
       </c>
       <c r="B39" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C39" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D39" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E39" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F39">
         <v>1.32</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="2">
+    <row r="40" spans="1:6">
+      <c r="A40" s="1">
         <v>46022</v>
       </c>
       <c r="B40" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C40" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D40" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E40" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F40">
         <v>15.32</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="2">
+    <row r="41" spans="1:6">
+      <c r="A41" s="1">
         <v>46022</v>
       </c>
       <c r="B41" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C41" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D41" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E41" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F41">
         <v>3.13</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="2">
+    <row r="42" spans="1:6">
+      <c r="A42" s="1">
         <v>46022</v>
       </c>
       <c r="B42" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C42" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D42" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E42" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F42">
         <v>9.91</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="2">
+    <row r="43" spans="1:6">
+      <c r="A43" s="1">
         <v>46022</v>
       </c>
       <c r="B43" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C43" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E43" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F43">
         <v>5.12</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="2">
+    <row r="44" spans="1:6">
+      <c r="A44" s="1">
         <v>46053</v>
       </c>
       <c r="B44" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C44" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D44" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E44" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F44">
-        <v>17.420000000000002</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="2">
+        <v>17.42</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="A45" s="1">
         <v>46053</v>
       </c>
       <c r="B45" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C45" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D45" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E45" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F45">
         <v>40.08</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="2">
+    <row r="46" spans="1:6">
+      <c r="A46" s="1">
         <v>46053</v>
       </c>
       <c r="B46" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C46" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D46" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E46" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F46">
         <v>0.09</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="2">
+    <row r="47" spans="1:6">
+      <c r="A47" s="1">
         <v>46053</v>
       </c>
       <c r="B47" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C47" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D47" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E47" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F47">
         <v>19.71</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="2">
+    <row r="48" spans="1:6">
+      <c r="A48" s="1">
         <v>46053</v>
       </c>
       <c r="B48" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C48" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D48" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E48" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F48">
         <v>0.09</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="2">
+    <row r="49" spans="1:6">
+      <c r="A49" s="1">
         <v>46053</v>
       </c>
       <c r="B49" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C49" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D49" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E49" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F49">
-        <v>18.350000000000001</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="2">
+        <v>18.35</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6">
+      <c r="A50" s="1">
         <v>46053</v>
       </c>
       <c r="B50" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C50" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E50" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F50">
         <v>4.26</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="2">
+    <row r="51" spans="1:6">
+      <c r="A51" s="1">
         <v>46081</v>
       </c>
       <c r="B51" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C51" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D51" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E51" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F51">
         <v>17.38</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="2">
+    <row r="52" spans="1:6">
+      <c r="A52" s="1">
         <v>46081</v>
       </c>
       <c r="B52" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C52" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D52" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E52" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F52">
         <v>41.97</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="2">
+    <row r="53" spans="1:6">
+      <c r="A53" s="1">
         <v>46081</v>
       </c>
       <c r="B53" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C53" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D53" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E53" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F53">
         <v>3.29</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="2">
+    <row r="54" spans="1:6">
+      <c r="A54" s="1">
         <v>46081</v>
       </c>
       <c r="B54" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C54" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D54" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E54" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F54">
         <v>16.57</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="2">
+    <row r="55" spans="1:6">
+      <c r="A55" s="1">
         <v>46081</v>
       </c>
       <c r="B55" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C55" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D55" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E55" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F55">
         <v>3.97</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="2">
+    <row r="56" spans="1:6">
+      <c r="A56" s="1">
         <v>46081</v>
       </c>
       <c r="B56" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C56" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D56" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E56" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F56">
         <v>13.08</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="2">
+    <row r="57" spans="1:6">
+      <c r="A57" s="1">
         <v>46081</v>
       </c>
       <c r="B57" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C57" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E57" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F57">
         <v>3.75</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="2">
+    <row r="58" spans="1:6">
+      <c r="A58" s="1">
         <v>46112</v>
       </c>
       <c r="B58" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C58" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D58" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E58" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F58">
         <v>24.21</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="2">
+    <row r="59" spans="1:6">
+      <c r="A59" s="1">
         <v>46112</v>
       </c>
       <c r="B59" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C59" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D59" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E59" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F59">
         <v>44.35</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="2">
+    <row r="60" spans="1:6">
+      <c r="A60" s="1">
         <v>46112</v>
       </c>
       <c r="B60" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C60" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D60" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E60" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F60">
         <v>0.1</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="2">
+    <row r="61" spans="1:6">
+      <c r="A61" s="1">
         <v>46112</v>
       </c>
       <c r="B61" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C61" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D61" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E61" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F61">
         <v>10.11</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="2">
+    <row r="62" spans="1:6">
+      <c r="A62" s="1">
         <v>46112</v>
       </c>
       <c r="B62" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C62" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D62" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E62" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F62">
         <v>0.1</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="2">
+    <row r="63" spans="1:6">
+      <c r="A63" s="1">
         <v>46112</v>
       </c>
       <c r="B63" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C63" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D63" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E63" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F63">
         <v>17.96</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="2">
+    <row r="64" spans="1:6">
+      <c r="A64" s="1">
         <v>46112</v>
       </c>
       <c r="B64" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C64" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E64" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F64">
         <v>3.17</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" s="2">
+    <row r="65" spans="1:6">
+      <c r="A65" s="1">
         <v>46142</v>
       </c>
       <c r="B65" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C65" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D65" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E65" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F65">
         <v>21.95</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="2">
+    <row r="66" spans="1:6">
+      <c r="A66" s="1">
         <v>46142</v>
       </c>
       <c r="B66" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C66" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D66" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E66" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F66">
-        <v>40.130000000000003</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="2">
+        <v>40.13</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="A67" s="1">
         <v>46142</v>
       </c>
       <c r="B67" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C67" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D67" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E67" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F67">
         <v>1.75</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="2">
+    <row r="68" spans="1:6">
+      <c r="A68" s="1">
         <v>46142</v>
       </c>
       <c r="B68" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C68" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D68" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E68" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F68">
         <v>16.78</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="2">
+    <row r="69" spans="1:6">
+      <c r="A69" s="1">
         <v>46142</v>
       </c>
       <c r="B69" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C69" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D69" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E69" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F69">
         <v>0.09</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="2">
+    <row r="70" spans="1:6">
+      <c r="A70" s="1">
         <v>46142</v>
       </c>
       <c r="B70" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C70" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D70" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E70" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F70">
         <v>16.62</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="2">
+    <row r="71" spans="1:6">
+      <c r="A71" s="1">
         <v>46142</v>
       </c>
       <c r="B71" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C71" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E71" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F71">
         <v>2.67</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="2">
+    <row r="72" spans="1:6">
+      <c r="A72" s="1">
         <v>46173</v>
       </c>
       <c r="B72" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C72" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D72" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E72" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F72">
-        <v>18.989999999999998</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73" s="2">
+        <v>18.99</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6">
+      <c r="A73" s="1">
         <v>46173</v>
       </c>
       <c r="B73" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C73" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D73" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E73" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F73">
         <v>44.19</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A74" s="2">
+    <row r="74" spans="1:6">
+      <c r="A74" s="1">
         <v>46173</v>
       </c>
       <c r="B74" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C74" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D74" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E74" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F74">
         <v>0.1</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A75" s="2">
+    <row r="75" spans="1:6">
+      <c r="A75" s="1">
         <v>46173</v>
       </c>
       <c r="B75" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C75" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D75" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E75" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F75">
         <v>17.88</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A76" s="2">
+    <row r="76" spans="1:6">
+      <c r="A76" s="1">
         <v>46173</v>
       </c>
       <c r="B76" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C76" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D76" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E76" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F76">
         <v>0.1</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A77" s="2">
+    <row r="77" spans="1:6">
+      <c r="A77" s="1">
         <v>46173</v>
       </c>
       <c r="B77" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C77" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D77" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E77" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F77">
         <v>16.13</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A78" s="2">
+    <row r="78" spans="1:6">
+      <c r="A78" s="1">
         <v>46173</v>
       </c>
       <c r="B78" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C78" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E78" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F78">
         <v>2.61</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A79" s="2">
+    <row r="79" spans="1:6">
+      <c r="A79" s="1">
         <v>46203</v>
       </c>
       <c r="B79" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C79" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D79" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E79" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F79">
         <v>23.92</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A80" s="2">
+    <row r="80" spans="1:6">
+      <c r="A80" s="1">
         <v>46203</v>
       </c>
       <c r="B80" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C80" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D80" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E80" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F80">
         <v>51.25</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A81" s="2">
+    <row r="81" spans="1:6">
+      <c r="A81" s="1">
         <v>46203</v>
       </c>
       <c r="B81" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C81" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D81" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E81" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F81">
         <v>0.68</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A82" s="2">
+    <row r="82" spans="1:6">
+      <c r="A82" s="1">
         <v>46203</v>
       </c>
       <c r="B82" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C82" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D82" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E82" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F82">
         <v>13.67</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A83" s="2">
+    <row r="83" spans="1:6">
+      <c r="A83" s="1">
         <v>46203</v>
       </c>
       <c r="B83" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C83" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D83" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E83" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F83">
         <v>0.64</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A84" s="2">
+    <row r="84" spans="1:6">
+      <c r="A84" s="1">
         <v>46203</v>
       </c>
       <c r="B84" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C84" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D84" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E84" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F84">
         <v>7.49</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A85" s="2">
+    <row r="85" spans="1:6">
+      <c r="A85" s="1">
         <v>46203</v>
       </c>
       <c r="B85" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C85" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E85" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F85">
         <v>2.35</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A86" s="2">
+    <row r="86" spans="1:6">
+      <c r="A86" s="1">
         <v>45869</v>
       </c>
       <c r="B86" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C86" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D86" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E86" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F86">
         <v>18.62</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A87" s="2">
+    <row r="87" spans="1:6">
+      <c r="A87" s="1">
         <v>45869</v>
       </c>
       <c r="B87" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C87" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D87" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E87" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F87">
         <v>4.8</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A88" s="2">
+    <row r="88" spans="1:6">
+      <c r="A88" s="1">
         <v>45869</v>
       </c>
       <c r="B88" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C88" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D88" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E88" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F88">
-        <v>4.1100000000000003</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A89" s="2">
+        <v>4.11</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6">
+      <c r="A89" s="1">
         <v>45869</v>
       </c>
       <c r="B89" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C89" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D89" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E89" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F89">
         <v>38.39</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A90" s="2">
+    <row r="90" spans="1:6">
+      <c r="A90" s="1">
         <v>45869</v>
       </c>
       <c r="B90" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C90" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D90" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E90" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F90">
         <v>2.91</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A91" s="2">
+    <row r="91" spans="1:6">
+      <c r="A91" s="1">
         <v>45869</v>
       </c>
       <c r="B91" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C91" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D91" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E91" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F91">
         <v>3.46</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A92" s="2">
+    <row r="92" spans="1:6">
+      <c r="A92" s="1">
         <v>45869</v>
       </c>
       <c r="B92" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C92" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D92" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E92" t="s">
+        <v>21</v>
+      </c>
+      <c r="F92">
+        <v>8.039999999999999</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6">
+      <c r="A93" s="1">
+        <v>45869</v>
+      </c>
+      <c r="B93" t="s">
+        <v>7</v>
+      </c>
+      <c r="C93" t="s">
+        <v>9</v>
+      </c>
+      <c r="D93" t="s">
         <v>20</v>
       </c>
-      <c r="F92">
-        <v>8.0399999999999991</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A93" s="2">
-        <v>45869</v>
-      </c>
-      <c r="B93" t="s">
-        <v>6</v>
-      </c>
-      <c r="C93" t="s">
-        <v>8</v>
-      </c>
-      <c r="D93" t="s">
-        <v>19</v>
-      </c>
       <c r="E93" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F93">
         <v>17.32</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A94" s="2">
+    <row r="94" spans="1:6">
+      <c r="A94" s="1">
         <v>45869</v>
       </c>
       <c r="B94" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C94" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E94" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F94">
         <v>2.34</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A95" s="2">
+    <row r="95" spans="1:6">
+      <c r="A95" s="1">
         <v>45900</v>
       </c>
       <c r="B95" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C95" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D95" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E95" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F95">
         <v>17.96</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A96" s="2">
+    <row r="96" spans="1:6">
+      <c r="A96" s="1">
         <v>45900</v>
       </c>
       <c r="B96" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C96" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D96" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E96" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F96">
         <v>6.69</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A97" s="2">
+    <row r="97" spans="1:6">
+      <c r="A97" s="1">
         <v>45900</v>
       </c>
       <c r="B97" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C97" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D97" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E97" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F97">
         <v>6.19</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A98" s="2">
+    <row r="98" spans="1:6">
+      <c r="A98" s="1">
         <v>45900</v>
       </c>
       <c r="B98" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C98" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D98" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E98" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F98">
-        <v>36.979999999999997</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A99" s="2">
+        <v>36.98</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6">
+      <c r="A99" s="1">
         <v>45900</v>
       </c>
       <c r="B99" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C99" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D99" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E99" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F99">
         <v>2.99</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A100" s="2">
+    <row r="100" spans="1:6">
+      <c r="A100" s="1">
         <v>45900</v>
       </c>
       <c r="B100" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C100" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D100" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E100" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F100">
         <v>5.88</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A101" s="2">
+    <row r="101" spans="1:6">
+      <c r="A101" s="1">
         <v>45900</v>
       </c>
       <c r="B101" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C101" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D101" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E101" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F101">
         <v>2.86</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A102" s="2">
+    <row r="102" spans="1:6">
+      <c r="A102" s="1">
         <v>45900</v>
       </c>
       <c r="B102" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C102" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D102" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E102" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F102">
         <v>14.75</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A103" s="2">
+    <row r="103" spans="1:6">
+      <c r="A103" s="1">
         <v>45900</v>
       </c>
       <c r="B103" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C103" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E103" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F103">
         <v>5.7</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A104" s="2">
+    <row r="104" spans="1:6">
+      <c r="A104" s="1">
         <v>45930</v>
       </c>
       <c r="B104" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C104" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D104" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E104" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F104">
         <v>19.03</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A105" s="2">
+    <row r="105" spans="1:6">
+      <c r="A105" s="1">
         <v>45930</v>
       </c>
       <c r="B105" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C105" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D105" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E105" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F105">
         <v>3.5</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A106" s="2">
+    <row r="106" spans="1:6">
+      <c r="A106" s="1">
         <v>45930</v>
       </c>
       <c r="B106" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C106" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D106" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E106" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F106">
         <v>5.8</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A107" s="2">
+    <row r="107" spans="1:6">
+      <c r="A107" s="1">
         <v>45930</v>
       </c>
       <c r="B107" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C107" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D107" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E107" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F107">
         <v>39.72</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A108" s="2">
+    <row r="108" spans="1:6">
+      <c r="A108" s="1">
         <v>45930</v>
       </c>
       <c r="B108" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C108" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D108" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E108" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F108">
         <v>0.1</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A109" s="2">
+    <row r="109" spans="1:6">
+      <c r="A109" s="1">
         <v>45930</v>
       </c>
       <c r="B109" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C109" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D109" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E109" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F109">
         <v>0.84</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A110" s="2">
+    <row r="110" spans="1:6">
+      <c r="A110" s="1">
         <v>45930</v>
       </c>
       <c r="B110" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C110" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D110" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E110" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F110">
         <v>6.66</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A111" s="2">
+    <row r="111" spans="1:6">
+      <c r="A111" s="1">
         <v>45930</v>
       </c>
       <c r="B111" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C111" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D111" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E111" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F111">
-        <v>20.399999999999999</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A112" s="2">
+        <v>20.4</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6">
+      <c r="A112" s="1">
         <v>45930</v>
       </c>
       <c r="B112" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C112" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E112" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F112">
         <v>3.95</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A113" s="2">
+    <row r="113" spans="1:6">
+      <c r="A113" s="1">
         <v>45961</v>
       </c>
       <c r="B113" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C113" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D113" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E113" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F113">
         <v>29.05</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A114" s="2">
+    <row r="114" spans="1:6">
+      <c r="A114" s="1">
         <v>45961</v>
       </c>
       <c r="B114" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C114" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D114" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E114" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F114">
         <v>8.43</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A115" s="2">
+    <row r="115" spans="1:6">
+      <c r="A115" s="1">
         <v>45961</v>
       </c>
       <c r="B115" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C115" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D115" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E115" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F115">
-        <v>1.1000000000000001</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A116" s="2">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6">
+      <c r="A116" s="1">
         <v>45961</v>
       </c>
       <c r="B116" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C116" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D116" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E116" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F116">
         <v>33.89</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A117" s="2">
+    <row r="117" spans="1:6">
+      <c r="A117" s="1">
         <v>45961</v>
       </c>
       <c r="B117" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C117" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D117" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E117" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F117">
         <v>3.46</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A118" s="2">
+    <row r="118" spans="1:6">
+      <c r="A118" s="1">
         <v>45961</v>
       </c>
       <c r="B118" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C118" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D118" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E118" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F118">
         <v>1.05</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A119" s="2">
+    <row r="119" spans="1:6">
+      <c r="A119" s="1">
         <v>45961</v>
       </c>
       <c r="B119" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C119" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D119" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E119" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F119">
         <v>4.57</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A120" s="2">
+    <row r="120" spans="1:6">
+      <c r="A120" s="1">
         <v>45961</v>
       </c>
       <c r="B120" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C120" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D120" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E120" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F120">
         <v>16.36</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A121" s="2">
+    <row r="121" spans="1:6">
+      <c r="A121" s="1">
         <v>45961</v>
       </c>
       <c r="B121" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C121" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E121" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F121">
         <v>2.09</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A122" s="2">
+    <row r="122" spans="1:6">
+      <c r="A122" s="1">
         <v>45991</v>
       </c>
       <c r="B122" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C122" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D122" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E122" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F122">
         <v>21.73</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A123" s="2">
+    <row r="123" spans="1:6">
+      <c r="A123" s="1">
         <v>45991</v>
       </c>
       <c r="B123" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C123" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D123" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E123" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F123">
         <v>7.04</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A124" s="2">
+    <row r="124" spans="1:6">
+      <c r="A124" s="1">
         <v>45991</v>
       </c>
       <c r="B124" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C124" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D124" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E124" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F124">
         <v>3.28</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A125" s="2">
+    <row r="125" spans="1:6">
+      <c r="A125" s="1">
         <v>45991</v>
       </c>
       <c r="B125" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C125" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D125" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E125" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F125">
-        <v>33.700000000000003</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A126" s="2">
+        <v>33.7</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6">
+      <c r="A126" s="1">
         <v>45991</v>
       </c>
       <c r="B126" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C126" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D126" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E126" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F126">
         <v>0.09</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A127" s="2">
+    <row r="127" spans="1:6">
+      <c r="A127" s="1">
         <v>45991</v>
       </c>
       <c r="B127" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C127" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D127" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E127" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F127">
         <v>1.71</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A128" s="2">
+    <row r="128" spans="1:6">
+      <c r="A128" s="1">
         <v>45991</v>
       </c>
       <c r="B128" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C128" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D128" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E128" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F128">
         <v>5.18</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A129" s="2">
+    <row r="129" spans="1:6">
+      <c r="A129" s="1">
         <v>45991</v>
       </c>
       <c r="B129" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C129" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D129" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E129" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F129">
         <v>22.2</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A130" s="2">
+    <row r="130" spans="1:6">
+      <c r="A130" s="1">
         <v>45991</v>
       </c>
       <c r="B130" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C130" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E130" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F130">
         <v>5.07</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A131" s="2">
+    <row r="131" spans="1:6">
+      <c r="A131" s="1">
         <v>46022</v>
       </c>
       <c r="B131" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C131" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D131" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E131" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F131">
         <v>22.63</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A132" s="2">
+    <row r="132" spans="1:6">
+      <c r="A132" s="1">
         <v>46022</v>
       </c>
       <c r="B132" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C132" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D132" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E132" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F132">
         <v>5.03</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A133" s="2">
+    <row r="133" spans="1:6">
+      <c r="A133" s="1">
         <v>46022</v>
       </c>
       <c r="B133" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C133" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D133" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E133" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F133">
         <v>0.1</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A134" s="2">
+    <row r="134" spans="1:6">
+      <c r="A134" s="1">
         <v>46022</v>
       </c>
       <c r="B134" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C134" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D134" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E134" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F134">
-        <v>34.979999999999997</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A135" s="2">
+        <v>34.98</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6">
+      <c r="A135" s="1">
         <v>46022</v>
       </c>
       <c r="B135" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C135" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D135" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E135" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F135">
         <v>0.1</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A136" s="2">
+    <row r="136" spans="1:6">
+      <c r="A136" s="1">
         <v>46022</v>
       </c>
       <c r="B136" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C136" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D136" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E136" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F136">
         <v>10.95</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A137" s="2">
+    <row r="137" spans="1:6">
+      <c r="A137" s="1">
         <v>46022</v>
       </c>
       <c r="B137" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C137" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D137" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E137" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F137">
         <v>2.63</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A138" s="2">
+    <row r="138" spans="1:6">
+      <c r="A138" s="1">
         <v>46022</v>
       </c>
       <c r="B138" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C138" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D138" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E138" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F138">
         <v>20.32</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A139" s="2">
+    <row r="139" spans="1:6">
+      <c r="A139" s="1">
         <v>46022</v>
       </c>
       <c r="B139" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C139" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E139" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F139">
         <v>3.27</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A140" s="2">
+    <row r="140" spans="1:6">
+      <c r="A140" s="1">
         <v>46053</v>
       </c>
       <c r="B140" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C140" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D140" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E140" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F140">
         <v>22.68</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A141" s="2">
+    <row r="141" spans="1:6">
+      <c r="A141" s="1">
         <v>46053</v>
       </c>
       <c r="B141" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C141" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D141" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E141" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F141">
-        <v>8.2799999999999994</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A142" s="2">
+        <v>8.279999999999999</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6">
+      <c r="A142" s="1">
         <v>46053</v>
       </c>
       <c r="B142" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C142" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D142" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E142" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F142">
         <v>3.31</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A143" s="2">
+    <row r="143" spans="1:6">
+      <c r="A143" s="1">
         <v>46053</v>
       </c>
       <c r="B143" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C143" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D143" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E143" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F143">
-        <v>38.200000000000003</v>
-      </c>
-    </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A144" s="2">
+        <v>38.2</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6">
+      <c r="A144" s="1">
         <v>46053</v>
       </c>
       <c r="B144" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C144" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D144" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E144" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F144">
         <v>0.1</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A145" s="2">
+    <row r="145" spans="1:6">
+      <c r="A145" s="1">
         <v>46053</v>
       </c>
       <c r="B145" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C145" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D145" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E145" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F145">
         <v>5.08</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A146" s="2">
+    <row r="146" spans="1:6">
+      <c r="A146" s="1">
         <v>46053</v>
       </c>
       <c r="B146" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C146" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D146" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E146" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F146">
         <v>3.8</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A147" s="2">
+    <row r="147" spans="1:6">
+      <c r="A147" s="1">
         <v>46053</v>
       </c>
       <c r="B147" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C147" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D147" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E147" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F147">
         <v>12.59</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A148" s="2">
+    <row r="148" spans="1:6">
+      <c r="A148" s="1">
         <v>46053</v>
       </c>
       <c r="B148" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C148" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E148" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F148">
         <v>5.97</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A149" s="2">
+    <row r="149" spans="1:6">
+      <c r="A149" s="1">
         <v>46081</v>
       </c>
       <c r="B149" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C149" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D149" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E149" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F149">
         <v>17.37</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A150" s="2">
+    <row r="150" spans="1:6">
+      <c r="A150" s="1">
         <v>46081</v>
       </c>
       <c r="B150" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C150" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D150" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E150" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F150">
         <v>11.66</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A151" s="2">
+    <row r="151" spans="1:6">
+      <c r="A151" s="1">
         <v>46081</v>
       </c>
       <c r="B151" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C151" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D151" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E151" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F151">
         <v>4.01</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A152" s="2">
+    <row r="152" spans="1:6">
+      <c r="A152" s="1">
         <v>46081</v>
       </c>
       <c r="B152" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C152" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D152" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E152" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F152">
         <v>33.22</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A153" s="2">
+    <row r="153" spans="1:6">
+      <c r="A153" s="1">
         <v>46081</v>
       </c>
       <c r="B153" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C153" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D153" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E153" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F153">
         <v>3.23</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A154" s="2">
+    <row r="154" spans="1:6">
+      <c r="A154" s="1">
         <v>46081</v>
       </c>
       <c r="B154" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C154" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D154" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E154" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F154">
         <v>7.66</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A155" s="2">
+    <row r="155" spans="1:6">
+      <c r="A155" s="1">
         <v>46081</v>
       </c>
       <c r="B155" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C155" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D155" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E155" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F155">
         <v>5.66</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A156" s="2">
+    <row r="156" spans="1:6">
+      <c r="A156" s="1">
         <v>46081</v>
       </c>
       <c r="B156" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C156" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D156" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E156" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F156">
         <v>13.7</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A157" s="2">
+    <row r="157" spans="1:6">
+      <c r="A157" s="1">
         <v>46081</v>
       </c>
       <c r="B157" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C157" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E157" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F157">
         <v>3.49</v>
       </c>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A158" s="2">
+    <row r="158" spans="1:6">
+      <c r="A158" s="1">
         <v>46112</v>
       </c>
       <c r="B158" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C158" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D158" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E158" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F158">
         <v>18.14</v>
       </c>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A159" s="2">
+    <row r="159" spans="1:6">
+      <c r="A159" s="1">
         <v>46112</v>
       </c>
       <c r="B159" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C159" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D159" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E159" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F159">
         <v>11.68</v>
       </c>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A160" s="2">
+    <row r="160" spans="1:6">
+      <c r="A160" s="1">
         <v>46112</v>
       </c>
       <c r="B160" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C160" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D160" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E160" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F160">
         <v>4.08</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A161" s="2">
+    <row r="161" spans="1:6">
+      <c r="A161" s="1">
         <v>46112</v>
       </c>
       <c r="B161" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C161" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D161" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E161" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F161">
         <v>28.57</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A162" s="2">
+    <row r="162" spans="1:6">
+      <c r="A162" s="1">
         <v>46112</v>
       </c>
       <c r="B162" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C162" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D162" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E162" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F162">
         <v>0.08</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A163" s="2">
+    <row r="163" spans="1:6">
+      <c r="A163" s="1">
         <v>46112</v>
       </c>
       <c r="B163" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C163" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D163" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E163" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F163">
-        <v>9.14</v>
-      </c>
-    </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A164" s="2">
+        <v>9.140000000000001</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6">
+      <c r="A164" s="1">
         <v>46112</v>
       </c>
       <c r="B164" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C164" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D164" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E164" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F164">
         <v>11.3</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A165" s="2">
+    <row r="165" spans="1:6">
+      <c r="A165" s="1">
         <v>46112</v>
       </c>
       <c r="B165" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C165" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D165" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E165" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F165">
         <v>14.29</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A166" s="2">
+    <row r="166" spans="1:6">
+      <c r="A166" s="1">
         <v>46112</v>
       </c>
       <c r="B166" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C166" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E166" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F166">
         <v>2.72</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A167" s="2">
+    <row r="167" spans="1:6">
+      <c r="A167" s="1">
         <v>46142</v>
       </c>
       <c r="B167" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C167" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D167" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E167" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F167">
         <v>25.94</v>
       </c>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A168" s="2">
+    <row r="168" spans="1:6">
+      <c r="A168" s="1">
         <v>46142</v>
       </c>
       <c r="B168" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C168" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D168" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E168" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F168">
         <v>1.72</v>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A169" s="2">
+    <row r="169" spans="1:6">
+      <c r="A169" s="1">
         <v>46142</v>
       </c>
       <c r="B169" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C169" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D169" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E169" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F169">
         <v>0.1</v>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A170" s="2">
+    <row r="170" spans="1:6">
+      <c r="A170" s="1">
         <v>46142</v>
       </c>
       <c r="B170" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C170" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D170" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E170" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F170">
         <v>41.51</v>
       </c>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A171" s="2">
+    <row r="171" spans="1:6">
+      <c r="A171" s="1">
         <v>46142</v>
       </c>
       <c r="B171" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C171" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D171" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E171" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F171">
         <v>0.7</v>
       </c>
     </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A172" s="2">
+    <row r="172" spans="1:6">
+      <c r="A172" s="1">
         <v>46142</v>
       </c>
       <c r="B172" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C172" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D172" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E172" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F172">
         <v>3.35</v>
       </c>
     </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A173" s="2">
+    <row r="173" spans="1:6">
+      <c r="A173" s="1">
         <v>46142</v>
       </c>
       <c r="B173" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C173" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D173" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E173" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F173">
         <v>4.82</v>
       </c>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A174" s="2">
+    <row r="174" spans="1:6">
+      <c r="A174" s="1">
         <v>46142</v>
       </c>
       <c r="B174" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C174" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D174" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E174" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F174">
-        <v>18.940000000000001</v>
-      </c>
-    </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A175" s="2">
+        <v>18.94</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6">
+      <c r="A175" s="1">
         <v>46142</v>
       </c>
       <c r="B175" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C175" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E175" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F175">
         <v>2.92</v>
       </c>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A176" s="2">
+    <row r="176" spans="1:6">
+      <c r="A176" s="1">
         <v>46173</v>
       </c>
       <c r="B176" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C176" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D176" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E176" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F176">
         <v>21.9</v>
       </c>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A177" s="2">
+    <row r="177" spans="1:6">
+      <c r="A177" s="1">
         <v>46173</v>
       </c>
       <c r="B177" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C177" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D177" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E177" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F177">
         <v>11.1</v>
       </c>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A178" s="2">
+    <row r="178" spans="1:6">
+      <c r="A178" s="1">
         <v>46173</v>
       </c>
       <c r="B178" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C178" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D178" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E178" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F178">
         <v>0.11</v>
       </c>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A179" s="2">
+    <row r="179" spans="1:6">
+      <c r="A179" s="1">
         <v>46173</v>
       </c>
       <c r="B179" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C179" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D179" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E179" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F179">
         <v>42.74</v>
       </c>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A180" s="2">
+    <row r="180" spans="1:6">
+      <c r="A180" s="1">
         <v>46173</v>
       </c>
       <c r="B180" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C180" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D180" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E180" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F180">
         <v>0.11</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A181" s="2">
+    <row r="181" spans="1:6">
+      <c r="A181" s="1">
         <v>46173</v>
       </c>
       <c r="B181" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C181" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D181" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E181" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F181">
         <v>0.11</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A182" s="2">
+    <row r="182" spans="1:6">
+      <c r="A182" s="1">
         <v>46173</v>
       </c>
       <c r="B182" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C182" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D182" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E182" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F182">
         <v>1.47</v>
       </c>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A183" s="2">
+    <row r="183" spans="1:6">
+      <c r="A183" s="1">
         <v>46173</v>
       </c>
       <c r="B183" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C183" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D183" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E183" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F183">
         <v>17.59</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A184" s="2">
+    <row r="184" spans="1:6">
+      <c r="A184" s="1">
         <v>46173</v>
       </c>
       <c r="B184" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C184" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E184" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F184">
-        <v>4.8600000000000003</v>
-      </c>
-    </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A185" s="2">
+        <v>4.86</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6">
+      <c r="A185" s="1">
         <v>46203</v>
       </c>
       <c r="B185" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C185" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D185" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E185" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F185">
         <v>11.71</v>
       </c>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A186" s="2">
+    <row r="186" spans="1:6">
+      <c r="A186" s="1">
         <v>46203</v>
       </c>
       <c r="B186" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C186" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D186" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E186" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F186">
         <v>6.56</v>
       </c>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A187" s="2">
+    <row r="187" spans="1:6">
+      <c r="A187" s="1">
         <v>46203</v>
       </c>
       <c r="B187" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C187" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D187" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E187" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F187">
         <v>1.4</v>
       </c>
     </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A188" s="2">
+    <row r="188" spans="1:6">
+      <c r="A188" s="1">
         <v>46203</v>
       </c>
       <c r="B188" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C188" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D188" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E188" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F188">
-        <v>34.619999999999997</v>
-      </c>
-    </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A189" s="2">
+        <v>34.62</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6">
+      <c r="A189" s="1">
         <v>46203</v>
       </c>
       <c r="B189" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C189" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D189" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E189" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F189">
         <v>7.13</v>
       </c>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A190" s="2">
+    <row r="190" spans="1:6">
+      <c r="A190" s="1">
         <v>46203</v>
       </c>
       <c r="B190" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C190" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D190" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E190" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F190">
         <v>5.72</v>
       </c>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A191" s="2">
+    <row r="191" spans="1:6">
+      <c r="A191" s="1">
         <v>46203</v>
       </c>
       <c r="B191" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C191" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D191" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E191" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F191">
         <v>11.58</v>
       </c>
     </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A192" s="2">
+    <row r="192" spans="1:6">
+      <c r="A192" s="1">
         <v>46203</v>
       </c>
       <c r="B192" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C192" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D192" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E192" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F192">
         <v>15.58</v>
       </c>
     </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A193" s="2">
+    <row r="193" spans="1:6">
+      <c r="A193" s="1">
         <v>46203</v>
       </c>
       <c r="B193" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C193" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E193" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F193">
         <v>5.7</v>
